--- a/Modèle cahier de paye_.xlsx
+++ b/Modèle cahier de paye_.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="27" documentId="8_{59FDAD53-62EF-4A93-9C18-5404A8482C3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB2698CB-FE44-4D5F-9E74-1B45846BF6FF}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="5" xr2:uid="{4D23B8DA-44E0-47C3-A68C-56B93911B776}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4D23B8DA-44E0-47C3-A68C-56B93911B776}"/>
   </bookViews>
   <sheets>
     <sheet name="JANV" sheetId="13" r:id="rId1"/>
